--- a/www/download/COUNTRY.DNK.WIOD16.xlsx
+++ b/www/download/COUNTRY.DNK.WIOD16.xlsx
@@ -342,7 +342,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AC37"/>
+  <dimension ref="A1:AC55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -500,7 +500,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>Dinamarca</t>
         </is>
       </c>
     </row>
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Standard v0.9</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -847,1848 +852,3409 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>exchange.r.us</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.038</t>
+          <t>8.05892687329755</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.039</t>
+          <t>8.31580085320117</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0.042</t>
+          <t>7.86974006248574</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0.051</t>
+          <t>6.57535687749453</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0.058</t>
+          <t>5.98504934673186</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>0.061</t>
+          <t>5.98662587778902</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0.064</t>
+          <t>5.94124112527107</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0.075</t>
+          <t>5.43602344013307</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>0.083</t>
+          <t>5.07318063059635</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>5.34659288368487</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>5.61371993151262</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>0.084</t>
+          <t>5.36364173922134</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>0.078</t>
+          <t>5.78928172381653</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>0.081</t>
+          <t>5.61466550630244</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>0.083</t>
+          <t>5.60304322183813</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Number of employee</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>2.736</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>2.754</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>2.754</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>2.735</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>2.712</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>2.756</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>2.816</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>2.877</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>2.911</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>2.825</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>2.759</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>2.757</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>2.741</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>2.745</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>2.765</t>
+          <t>surplus_value.empe_hs.r.pc</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>2.521</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>2.548</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>2.543</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>2.526</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>2.514</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>2.557</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>2.615</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>2.675</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>2.708</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>2.631</t>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>2.569</t>
-        </is>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>2.567</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>2.55</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>2.554</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>2.575</t>
+          <t>surplus_value.empe_ms.r.pc</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>3941.134</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>3985.871</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>3958.902</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>3907.52</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>3886.552</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>3939.068</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>4041.838</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>4083.314</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>4133.763</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>3986.916</t>
-        </is>
-      </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>3872.712</t>
-        </is>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>3917.698</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>3853.532</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>3914.671</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>3951.917</t>
+          <t>surplus_value.empe_ls.r.pc</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>gross_output.s.mv</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>3625.842</t>
+          <t>6570588188.40115</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>3682.792</t>
+          <t>6689805032.66884</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>3651.101</t>
+          <t>6744479330.37906</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>3607.169</t>
+          <t>7397577931.72513</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>3600.217</t>
+          <t>7605967124.91041</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>3651.787</t>
+          <t>7741496410.79421</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>3752.763</t>
+          <t>7289559454.20061</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>3795.767</t>
+          <t>7612105552.79584</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>3845.516</t>
+          <t>8101567664.94727</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>3715.175</t>
+          <t>7110107926.37437</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>3606.58</t>
+          <t>6529959230.77392</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>3649.161</t>
+          <t>6827232501.0354</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>3587.407</t>
+          <t>6714511341.31478</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>3643.337</t>
+          <t>7084067848.55317</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>3681.438</t>
+          <t>6850879489.43208</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>2973257803.126</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>3062356960.32338</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>3065712856.69255</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>3584487499.57961</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>3530419025.25489</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>3614729506.68733</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>3554149703.42512</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>3452948919.0312</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>3530991773.55852</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>3287903127.74136</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>3050924187.26731</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>2994216007.88656</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>2764422291.38279</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>2508339907.46308</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>2666936245.48453</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>1338641.23791</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1321528.12698242</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>1244183.47935909</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>1137544.45099415</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>1079306.23621455</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>1011257.45346244</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>898084.715174551</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>787839.506653782</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>732223.721738077</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>772576.989638607</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>743373.554084735</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>694309.626342624</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>691980.064723317</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>685648.066634516</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>678808.318828958</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>17571.4008402287</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>17564.8895990677</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>17454.061734434</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>18546.9477321114</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>20223.4237963941</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>21808.7818387638</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>23489.0840209087</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>26436.1922360352</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>28736.6835718399</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>25105.0496467329</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>26757.1262880672</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>28608.6026205058</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>27374.3778536699</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>27438.1381465454</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>27834.9829202821</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>53388.434953538</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>53846.1985891745</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>54612.0981228939</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>65189.451696275</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>74102.3868837519</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>80979.7764488889</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>80555.5797311417</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>94976.9654460105</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>109716.617898298</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>87626.9251455449</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>89159.0296624006</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>98994.3460335095</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>94862.6219083646</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>99984.2386974088</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>97140.9450089368</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>0.219484565444642</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>0.202600496191374</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>0.190946827270379</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>0.00632768294576391</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>0.0197704505459007</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>0.0102518025883036</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>0.0558820852097119</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>0.0992826969085283</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>0.0890753212161983</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>0.129952694972543</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>0.182127046962246</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>0.218736721194582</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>0.297705857452606</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>0.452489349294308</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>0.380399702555005</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>38334.2109255016</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>39072.7560886336</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>42138.0220816801</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>51398.5574952465</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>58347.4079533161</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>60736.2429786984</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>64503.8787533082</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>75178.0499043001</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>83175.367746906</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>79553.4943680614</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>80403.8000179726</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>83788.3533798052</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>78278.8534861239</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>81199.192412883</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>82770.468919583</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>labour_force_value.m.mv</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>8.05892687329755</t>
+          <t>1179.39619322729</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>8.31580085320117</t>
+          <t>1201.86693890242</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>7.86974006248574</t>
+          <t>1205.54968804268</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>6.57535687749453</t>
+          <t>1419.03701487712</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>5.98504934673186</t>
+          <t>1404.30351044347</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>5.98662587778902</t>
+          <t>1413.66034676861</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>5.94124112527107</t>
+          <t>1359.13946593695</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>5.43602344013307</t>
+          <t>1290.82202580605</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>5.07318063059635</t>
+          <t>1303.91129008808</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>5.34659288368487</t>
+          <t>1249.67811772762</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>5.61371993151262</t>
+          <t>1187.59213206201</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>5.36364173922134</t>
+          <t>1166.42618149068</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>5.78928172381653</t>
+          <t>1084.08717309129</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>5.61466550630244</t>
+          <t>982.122125083432</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>5.60304322183813</t>
+          <t>1035.70339630467</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Value transfer through trade</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>trade_transfers.s.mv</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>0.082</t>
+          <t>4726752531.27449</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0.084</t>
+          <t>4914701929.51575</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>0.092</t>
+          <t>5051432924.68251</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>0.113</t>
+          <t>6032332364.76863</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0.127</t>
+          <t>5950394993.2957</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>0.134</t>
+          <t>6088437356.73703</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>0.143</t>
+          <t>5629977457.59408</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>0.166</t>
+          <t>5199274574.91663</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>0.187</t>
+          <t>5439664771.03108</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>0.177</t>
+          <t>5062820872.80615</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>5016258241.47445</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>4942152766.94972</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>0.169</t>
+          <t>4791407282.97461</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>0.176</t>
+          <t>4958010820.81753</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>0.181</t>
+          <t>4995116003.40874</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Value transfer through trade of productive sectors</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>trade_transfers.p.s.mv</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>0.088</t>
+          <t>4916957177.56651</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>5090729345.32942</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>0.098</t>
+          <t>5240325007.99917</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>0.121</t>
+          <t>6246129101.81334</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>0.136</t>
+          <t>6351050888.06127</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>0.143</t>
+          <t>6597147179.77741</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>0.153</t>
+          <t>6289844757.56074</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>0.177</t>
+          <t>6183657422.00331</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>6206040432.30659</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>0.188</t>
+          <t>5623716849.72355</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>0.181</t>
+          <t>5743746262.65342</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>0.192</t>
+          <t>5929171354.22509</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>5789271589.38291</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>0.188</t>
+          <t>5841056866.90946</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>0.193</t>
+          <t>5782446581.18816</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Value transfer through trade of unproductive sectors</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>trade_transfers.u.s.mv</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>0.515</t>
+          <t>-190204646.292022</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>0.526</t>
+          <t>-176027415.813668</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>-188892083.316658</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>0.708</t>
+          <t>-213796737.044713</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>0.801</t>
+          <t>-400655894.765574</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>0.836</t>
+          <t>-508709823.040387</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>0.907</t>
+          <t>-659867299.966661</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>1.048</t>
+          <t>-984382847.086685</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>1.159</t>
+          <t>-766375661.275515</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>1.035</t>
+          <t>-560895976.917399</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>1.024</t>
+          <t>-727488021.178973</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>1.104</t>
+          <t>-987018587.275366</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>1.045</t>
+          <t>-997864306.408298</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>1.091</t>
+          <t>-883046046.091927</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>1.115</t>
+          <t>-787330577.779428</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Working day of employee per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>abstract_labour.empe.m.mv</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>0.274</t>
+          <t>1438.25545418485</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>0.279</t>
+          <t>1445.36577708006</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>0.301</t>
+          <t>1435.74557609123</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>0.363</t>
+          <t>1428.01623119557</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>0.417</t>
+          <t>1432.06722354813</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>1428.15291357059</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>0.492</t>
+          <t>1435.09101338432</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>0.569</t>
+          <t>1418.97831775701</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>0.642</t>
+          <t>1420.0576070901</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>1412.07715697453</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>0.554</t>
+          <t>1403.88478007007</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>0.606</t>
+          <t>1421.56641994546</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>0.581</t>
+          <t>1406.8262745098</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>0.601</t>
+          <t>1426.52192638998</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>0.615</t>
+          <t>1429.68466019417</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>abstract_labour.emp.m.mv</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>0.142</t>
+          <t>1440.47307643422</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>0.142</t>
+          <t>1447.30235741775</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>0.154</t>
+          <t>1437.50986097927</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>0.188</t>
+          <t>1428.70946770608</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0.216</t>
+          <t>1433.09434655679</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>0.225</t>
+          <t>1429.26978902485</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>0.241</t>
+          <t>1435.3118692174</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>0.271</t>
+          <t>1419.29587020833</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>0.304</t>
+          <t>1420.04914708018</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>0.276</t>
+          <t>1411.29784850984</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>0.276</t>
+          <t>1403.66504401326</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>0.295</t>
+          <t>1421.00048621327</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>1405.88547234765</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>0.293</t>
+          <t>1426.10951250316</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>1429.26460048458</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Total exports (USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>68937.2861514144</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>70004.5890342316</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>74419.3725341988</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>88417.4976250317</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>101369.062878022</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>116659.693629372</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>131971.40890363</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>152749.703601894</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>176408.366129477</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>137642.012753855</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>147250.376993731</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>165532.647964842</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>161194.083286859</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>169171.484812651</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>170292.919873152</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Total exports (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>2316637425.9549</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>2353073317.46299</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>2392483489.81998</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>2693797595.71963</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>2768996940.14232</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>2915614055.86926</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>2829807108.78778</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>2908626178.22817</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>3227273566.58061</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>2640639615.16837</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>2520005587.92122</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>2727399346.13357</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>2652411972.87135</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>2881902053.03455</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>2738937239.89406</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Total imports (USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>55301.5132364795</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>55876.4694613352</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>59950.0315722462</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>70020.3627645226</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>83583.4768377555</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>97458.2473564151</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>115960.615652451</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>136980.449422543</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>156746.407817367</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>116919.394735237</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>121468.180861832</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>140187.973167586</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>137156.987544038</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>142334.691143235</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>143554.461961723</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Total imports (magnitude of value)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>imports.s.mv</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>3941.134</t>
+          <t>4936650109.8371</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>3985.871</t>
+          <t>5006006151.50382</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>3958.902</t>
+          <t>5107471410.8979</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>3907.52</t>
+          <t>5927068732.01315</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>3886.552</t>
+          <t>6265070231.49905</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>3939.068</t>
+          <t>6582901327.10493</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>4041.838</t>
+          <t>6622274595.74484</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>4083.314</t>
+          <t>6565656638.30393</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>4133.763</t>
+          <t>6974211166.9452</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>3986.916</t>
+          <t>5686116929.95788</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>3872.712</t>
+          <t>5306547855.7289</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>3917.698</t>
+          <t>5590038691.011</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>3853.532</t>
+          <t>5450445713.96137</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>3914.671</t>
+          <t>5601989873.20759</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>3951.917</t>
+          <t>5526096553.75519</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Trade balance (USD)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>trade_balance.s.us</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>3625.842</t>
+          <t>13635.772914935</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>3682.792</t>
+          <t>14128.1195728963</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>3651.101</t>
+          <t>14469.3409619525</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>3607.169</t>
+          <t>18397.1348605091</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>3600.217</t>
+          <t>17785.5860402662</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>3651.787</t>
+          <t>19201.4462729569</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>3752.763</t>
+          <t>16010.7932511788</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>3795.767</t>
+          <t>15769.2541793514</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>3845.516</t>
+          <t>19661.9583121098</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>3715.175</t>
+          <t>20722.6180186175</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>3606.58</t>
+          <t>25782.1961318996</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>3649.161</t>
+          <t>25344.6747972561</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>3587.407</t>
+          <t>24037.0957428212</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>3643.337</t>
+          <t>26836.7936694162</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>3681.438</t>
+          <t>26738.4579114289</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Trade balance (magnitude of value)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>trade_balance.s.mv</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>6570.85</t>
+          <t>-2620012683.88221</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>6690.194</t>
+          <t>-2652932834.04082</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>6745.562</t>
+          <t>-2714987921.07792</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>7398.797</t>
+          <t>-3233271136.29352</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>7607.343</t>
+          <t>-3496073291.35673</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>7739.993</t>
+          <t>-3667287271.23567</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>7290.121</t>
+          <t>-3792467486.95706</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>7614.709</t>
+          <t>-3657030460.07576</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>8104.414</t>
+          <t>-3746937600.36459</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>7110.884</t>
+          <t>-3045477314.78951</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>6530.37</t>
+          <t>-2786542267.80768</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>6829.501</t>
+          <t>-2862639344.87743</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>6715.798</t>
+          <t>-2798033741.09002</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>7084.672</t>
+          <t>-2720087820.17304</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>6853.431</t>
+          <t>-2787159313.86112</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>gdp.p.s.us</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>0.053</t>
+          <t>70855.463634</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0.054</t>
+          <t>70457.074471</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0.055</t>
+          <t>75506.178766</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>0.065</t>
+          <t>91283.410343</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0.074</t>
+          <t>105320.601967</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>0.081</t>
+          <t>109281.256814</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>0.081</t>
+          <t>116019.19287</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>0.095</t>
+          <t>129469.6404</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>144063.86313</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>0.088</t>
+          <t>125008.20888</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>0.089</t>
+          <t>127521.680585</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>0.099</t>
+          <t>135205.471364727</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>0.095</t>
+          <t>130302.520414</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>135097.27323</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>0.097</t>
+          <t>138088.843184019</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Rate of profit</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>appropriated_profit.r.pc</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2162.536</t>
+          <t>0.0297956906518019</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>2182.247</t>
+          <t>0.0253846881864294</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>2155.54</t>
+          <t>0.0236280635452647</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>2104.673</t>
+          <t>0.0222204812483701</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>2075.759</t>
+          <t>0.0261372713138944</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2084.874</t>
+          <t>0.0257239151319904</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>2125.552</t>
+          <t>0.0258462530935462</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>2118.778</t>
+          <t>0.018196423015501</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>2121.941</t>
+          <t>0.018151210474344</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>2037.041</t>
+          <t>0.00813776419040734</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>1959.677</t>
+          <t>0.014421647817932</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>1973.018</t>
+          <t>0.0170542069567297</t>
         </is>
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>1937.597</t>
+          <t>0.0211384459733628</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>1944.043</t>
+          <t>0.0214241776712619</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>1963.066</t>
+          <t>0.0212894191578088</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>compensation.empe.s.us</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>82179.05565</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>83804.676459</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>91763.513695</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>112710.688379</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>127482.324004</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>0.022</t>
+          <t>133787.381465</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>0.023</t>
+          <t>142893.543975</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>0.026</t>
+          <t>166047.481204</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>0.029</t>
+          <t>187223.966415</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>0.025</t>
+          <t>176874.697695</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>0.027</t>
+          <t>169882.00545</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>0.029</t>
+          <t>180356.642222817</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>0.027</t>
+          <t>168849.616694</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>0.027</t>
+          <t>176314.68854</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>0.028</t>
+          <t>181400.783658557</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>compensation.emp.s.us</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2973.427</t>
+          <t>88180.226868</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>3062.561</t>
+          <t>89605.32042</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>3066.117</t>
+          <t>98345.433757</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>3584.796</t>
+          <t>120821.122686</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>3530.533</t>
+          <t>136345.742988</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>3614.691</t>
+          <t>142950.806927</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>3554.276</t>
+          <t>152593.537425</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>3453.607</t>
+          <t>177175.836456</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>3531.379</t>
+          <t>199645.365255</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>3288.097</t>
+          <t>188274.106875</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>3051.191</t>
+          <t>181025.240375</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>2994.603</t>
+          <t>192282.708206817</t>
         </is>
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>2764.633</t>
+          <t>180109.044566</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>2508.335</t>
+          <t>188102.03365</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>2666.981</t>
+          <t>193361.283482557</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>capital_stock.s.us</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>21.94</t>
+          <t>514524.956634</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>20.25</t>
+          <t>526100.86235</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>19.08</t>
+          <t>570323.157355</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>0.62</t>
+          <t>707835.496493</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>800956.303329</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>836391.500357</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>5.58</t>
+          <t>906993.822735</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>9.91</t>
+          <t>1047668.4037</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>8.9</t>
+          <t>1159038.56538</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>12.99</t>
+          <t>1035315.222315</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>18.2</t>
+          <t>1023709.42443</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>21.86</t>
+          <t>1104155.06244245</t>
         </is>
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>29.76</t>
+          <t>1044553.070396</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>45.25</t>
+          <t>1091189.13551</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>38.04</t>
+          <t>1115378.66927521</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Total real wage (constant USD)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>compensation.emp.s.cu</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>1.339</t>
+          <t>112968.769449193</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>1.322</t>
+          <t>115006.905752525</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>1.244</t>
+          <t>115907.470358158</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>1.138</t>
+          <t>117048.23577598</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>117415.391156044</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>1.011</t>
+          <t>121448.246952031</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>0.898</t>
+          <t>125980.496275759</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>0.788</t>
+          <t>129592.016657445</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>0.733</t>
+          <t>130592.015444097</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>0.773</t>
+          <t>129611.899529727</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>0.743</t>
+          <t>126099.29535</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>0.695</t>
+          <t>128091.096243496</t>
         </is>
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>0.692</t>
+          <t>127291.155885371</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>0.686</t>
+          <t>127620.790331099</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>0.679</t>
+          <t>130201.042323482</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>105539.747746929</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>107757.969832309</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>108264.828607845</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>109175.686952057</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>109830.533255867</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>113535.432796336</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>117937.26795127</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>121449.926396707</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>122483.384351022</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>121843.437503117</t>
+        </is>
+      </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>118337.09562</t>
+        </is>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>120447.198510064</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>119577.196322117</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>119750.489172559</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>122226.776367662</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>53664.837366</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>52427.662434</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>55613.653885</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>67127.002872</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>79282.220164</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>82251.506951</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>87946.27065</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>94241.867358</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>104213.320695</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>87978.64551</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>95167.376805</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>102618.842327019</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>100359.082131</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>104577.022325</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>106516.232929462</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour (employee only)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>3625842000</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>3682792000</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>3651101000</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>3607169000</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>3600217000</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>3651787000</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>3752763000</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>3795767000</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>3845516000</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>3715175000</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>3606580000</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>3649161000</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>3587407000</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>3643337000</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>3681438000</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>3941134337.12402</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>3985870692.32848</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>3958902157.13691</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>3907520394.17614</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>3886551867.86201</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>3939067538.55247</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>4041838223.71621</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>4083314218.58938</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>4133763067.15041</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>3986916422.04031</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>3872711856.43258</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>3917698340.49</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>3853532079.7049</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>3914670611.82118</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>3951916620.33987</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>2162536491.5631</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>2182246656.53073</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>2155539937.94832</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>2104673189.81556</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>2075759000.71623</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>2084873702.20321</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>2125552011.00408</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>2118777798.06614</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>2121940968.31571</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>2037040694.84096</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>1959677493.74723</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>1973017545.40415</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>1937597410.46853</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>1944042729.13806</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>1963066280.23548</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Number of persons engaged</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>2736000</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>2754000</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>2754000</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>2735000</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>2712000</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>2756000</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>2816000</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>2877000</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>2911000</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>2825000</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>2759000</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>2757000</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>2741000</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>2745000</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>2765000</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Number of employee</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>2521000</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>2548000</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>2543000</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>2526000</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>2514000</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>2557000</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>2615000</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>2675000</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>2708000</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>2631000</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>2569000</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>2567000</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>2550000</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>2554000</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>2575000</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total hours worked by persons engaged</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>3941134337.12402</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>3985870692.32848</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>3958902157.13691</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>3907520394.17614</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>3886551867.86201</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>3939067538.55247</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>4041838223.71621</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>4083314218.58938</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>4133763067.15041</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>3986916422.04031</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>3872711856.43258</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>3917698340.49</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>3853532079.7049</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>3914670611.82118</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>3951916620.33987</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total hours worked by employees</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>3625842000</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>3682792000</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>3651101000</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>3607169000</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>3600217000</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>3651787000</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>3752763000</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>3795767000</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>3845516000</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>3715175000</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>3606580000</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>3649161000</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>3587407000</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>3643337000</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>3681438000</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Share of high-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Share of medium-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Share of low-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Share of hours worked by high-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Share of hours worked by low-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Gross output (USD)</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>273742.650192</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>278889.915829</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>300689.346943</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>363470.157518</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>416795.059737</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>450289.704924</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>492037.93254</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>568886.803756</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>642214.07382</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>559835.593455</t>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>553719.46551</t>
+        </is>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>606152.632302</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>580801.584792</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>601457.0229</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>614581.853431</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (USD)</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>141845.064234</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>142032.862601</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>153959.087642</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>187948.125558</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>215627.963152</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>225202.480917</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>240539.808075</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>271418.07173</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>303858.68595</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>276252.93942</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>276192.439045</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>294901.550396727</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>280468.126697</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>292679.055975</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>299877.694863019</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>capital_stock.s.cu</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>675039.79452526</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>689131.132010848</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>694878.087898715</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>706892.163402758</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>710844.159887436</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>717184.827988182</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>742609.773646155</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>763796.672373153</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>754654.05724291</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>713539.339227846</t>
+        </is>
+      </c>
+      <c r="R55" t="inlineStr">
+        <is>
+          <t>713099.658348</t>
+        </is>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>717403.291498887</t>
+        </is>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>715730.130985484</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>715711.048185458</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>721302.544150174</t>
         </is>
       </c>
     </row>
@@ -2699,7 +4265,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2722,36 +4288,51 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Hours of abstract labour</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Hours of abstract labour (employee only)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Number of persons engaged</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -2763,331 +4344,695 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Total hours worked by persons engaged</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Total hours worked by employees</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Share of hours worked by high-skilled persons engaged</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Share of hours worked by low-skilled persons engaged</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Share of high-skilled labour compensation</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Share of medium-skilled labour compensation</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Share of low-skilled labour compensation</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>compensation.empe.s.us</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>compensation.emp.s.us</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>labour_force_value.m.mv</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>capital_stock.s.us</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>surplus_value.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>surplus_value.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>surplus_value.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Gross output (USD)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>gross_output.s.mv</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Complex labour multiplier</t>
+          <t>Gross Domestic Product (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.emp.r.un</t>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Complex labour multiplier (employee only)</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.empe.r.un</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Gross Domestic Product (USD)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>exchange.r.us</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Complex labour multiplier</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>complex_labour_multiplier.emp.r.un</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Complex labour multiplier (employee only)</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>complex_labour_multiplier.empe.r.un</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Working day of employee per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.m.mv</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Magnitude of value "created" by employee in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.m.mv</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Magnitude of value created by persons engaged in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Total exports (USD)</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Total exports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total imports (USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total imports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>imports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Trade balance (USD)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>trade_balance.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Trade balance (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>trade_balance.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Value transfer through trade</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>trade_transfers.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of productive sectors</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>trade_transfers.p.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of unproductive sectors</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>trade_transfers.u.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total real wage (constant USD)</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>compensation.emp.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>gdp.p.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Rate of profit</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>appropriated_profit.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3124,6 +5069,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Standard v0.9</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>WIOD16</t>
